--- a/artfynd/A 14086-2025 artfynd.xlsx
+++ b/artfynd/A 14086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081561</v>
+        <v>125081591</v>
       </c>
       <c r="B2" t="n">
-        <v>58371</v>
+        <v>103702</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,32 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>220461</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>larv</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -764,7 +763,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Många i kärret N vigen</t>
+          <t>Talrikt blommande på vägen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081591</v>
+        <v>125081561</v>
       </c>
       <c r="B3" t="n">
-        <v>103702</v>
+        <v>58371</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,31 +807,32 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220461</v>
+        <v>208250</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>larv</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Talrikt blommande på vägen</t>
+          <t>Många i kärret N vigen</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14086-2025 artfynd.xlsx
+++ b/artfynd/A 14086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081591</v>
+        <v>125081561</v>
       </c>
       <c r="B2" t="n">
-        <v>103702</v>
+        <v>58371</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220461</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>larv</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -763,7 +764,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Talrikt blommande på vägen</t>
+          <t>Många i kärret N vigen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081561</v>
+        <v>125081591</v>
       </c>
       <c r="B3" t="n">
-        <v>58371</v>
+        <v>103702</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,32 +808,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>220461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>larv</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Många i kärret N vigen</t>
+          <t>Talrikt blommande på vägen</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14086-2025 artfynd.xlsx
+++ b/artfynd/A 14086-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081591</v>
+        <v>125081561</v>
       </c>
       <c r="B2" t="n">
-        <v>103702</v>
+        <v>58485</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,32 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220461</v>
+        <v>208250</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Åkergroda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Rana arvalis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>With.</t>
+          <t>Nilsson, 1842</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>larv</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -763,7 +764,7 @@
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Talrikt blommande på vägen</t>
+          <t>Många i kärret N vigen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081561</v>
+        <v>125081591</v>
       </c>
       <c r="B3" t="n">
-        <v>58371</v>
+        <v>103874</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -807,32 +808,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208250</v>
+        <v>220461</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Skogsbräsma</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Cardamine flexuosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
+          <t>With.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>larv</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -880,7 +880,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Många i kärret N vigen</t>
+          <t>Talrikt blommande på vägen</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 14086-2025 artfynd.xlsx
+++ b/artfynd/A 14086-2025 artfynd.xlsx
@@ -785,7 +785,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -901,7 +901,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Sven Halling, Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 14086-2025 artfynd.xlsx
+++ b/artfynd/A 14086-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>125081561</v>
       </c>
       <c r="B2" t="n">
-        <v>58485</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58505</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +780,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -795,12 +790,7 @@
         <v>125081591</v>
       </c>
       <c r="B3" t="n">
-        <v>103874</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -901,7 +891,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Sven Halling, Magnus Kasselstrand</t>
+          <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 14086-2025 artfynd.xlsx
+++ b/artfynd/A 14086-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,57 +675,77 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125081561</v>
+        <v>116792523</v>
       </c>
       <c r="B2" t="n">
-        <v>58505</v>
+        <v>56879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208250</v>
+        <v>100070</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Åkergroda</t>
+          <t>Sandödla</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rana arvalis</t>
+          <t>Lacerta agilis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Nilsson, 1842</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>larv</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>i lekdräkt</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>570971</v>
+        <v>571083</v>
       </c>
       <c r="R2" t="n">
-        <v>6427699</v>
+        <v>6427672</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,17 +769,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Många i kärret N vigen</t>
+          <t>2024-05-10</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +790,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand</t>
+          <t>Lennart Schüssler</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Sven Halling</t>
+          <t>Lennart Schüssler</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125081591</v>
+        <v>101404560</v>
       </c>
       <c r="B3" t="n">
-        <v>103929</v>
+        <v>56895</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,45 +813,54 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220461</v>
+        <v>100088</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogsbräsma</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cardamine flexuosa</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>With.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>årsunge</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>570971</v>
+        <v>571083</v>
       </c>
       <c r="R3" t="n">
-        <v>6427699</v>
+        <v>6427672</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,17 +884,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
+          <t>2022-06-04</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-14</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Talrikt blommande på vägen</t>
+          <t>2022-06-04</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,15 +915,1968 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>126117384</v>
+      </c>
+      <c r="B4" t="n">
+        <v>9406</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>101246</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ekoxe</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lucanus cervus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>frispringande/krypande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-21</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>102519412</v>
+      </c>
+      <c r="B5" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2022-07-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126640313</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-05</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Kraschade in i ett fönster men kunde flyga iväg igen efter en stund i handen.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>100326473</v>
+      </c>
+      <c r="B7" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-04-29</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102782321</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58112</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-01</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102301998</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58602</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103042</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grönfink</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Chloris chloris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-07-17</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Två vuxna med tre ungar i släptåg. Fick med fyra på bild.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>109148845</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2023-05-14</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>13:45</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127425950</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-12</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>102762957</v>
+      </c>
+      <c r="B12" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2022-08-08</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>22:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>102377411</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-07-21</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127426459</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-01</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125081561</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58815</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>208250</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Åkergroda</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Rana arvalis</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Nilsson, 1842</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>larv</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>570971</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6427699</v>
+      </c>
+      <c r="S15" t="n">
+        <v>50</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Många i kärret N vigen</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Magnus Kasselstrand, Sven Halling</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>100011947</v>
+      </c>
+      <c r="B16" t="n">
+        <v>56884</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>208255</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Skogsödla</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Zootoca vivipara</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Jacquin, 1787)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2022-03-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2022-03-27</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111057748</v>
+      </c>
+      <c r="B17" t="n">
+        <v>56876</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>208257</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kopparödla</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Anguis fragilis</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-07-24</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>101460261</v>
+      </c>
+      <c r="B18" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Dalhem Hagaberg, Västervik, Sm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>571083</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6427672</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2022-06-06</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lennart Schüssler</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>125081591</v>
+      </c>
+      <c r="B19" t="n">
+        <v>104803</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220461</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogsbräsma</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Cardamine flexuosa</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>With.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>A 14086, Hagaberg, Dalhem, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>570971</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6427699</v>
+      </c>
+      <c r="S19" t="n">
+        <v>50</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Dalhem</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-05-14</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Talrikt blommande på vägen</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Sven Halling</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
